--- a/artfynd/A 48673-2023 artfynd.xlsx
+++ b/artfynd/A 48673-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55934766</v>
+        <v>55934777</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>643503.0382949202</v>
+        <v>643522</v>
       </c>
       <c r="R2" t="n">
-        <v>7333437.154822675</v>
+        <v>7333138</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>2014-08-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-08-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>55934768</v>
+        <v>55934778</v>
       </c>
       <c r="B3" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>643503.0382949202</v>
+        <v>643522</v>
       </c>
       <c r="R3" t="n">
-        <v>7333437.154822675</v>
+        <v>7333138</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -860,19 +840,9 @@
           <t>2014-08-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-08-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>55934779</v>
+        <v>55934768</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>643521.8598776778</v>
+        <v>643503</v>
       </c>
       <c r="R4" t="n">
-        <v>7333138.117257788</v>
+        <v>7333437</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -972,19 +937,9 @@
           <t>2014-08-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2014-08-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>55934777</v>
+        <v>55934767</v>
       </c>
       <c r="B5" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>643521.8598776778</v>
+        <v>643503</v>
       </c>
       <c r="R5" t="n">
-        <v>7333138.117257788</v>
+        <v>7333437</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1084,19 +1034,9 @@
           <t>2014-08-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2014-08-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>55934769</v>
+        <v>55934779</v>
       </c>
       <c r="B6" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>643689.1001909398</v>
+        <v>643522</v>
       </c>
       <c r="R6" t="n">
-        <v>7333290.90956175</v>
+        <v>7333138</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1196,19 +1131,9 @@
           <t>2014-08-19</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2014-08-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>55934778</v>
+        <v>55934771</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>643521.8598776778</v>
+        <v>643689</v>
       </c>
       <c r="R7" t="n">
-        <v>7333138.117257788</v>
+        <v>7333291</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1308,19 +1228,9 @@
           <t>2014-08-19</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2014-08-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>55934771</v>
+        <v>55934776</v>
       </c>
       <c r="B8" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>643689.1001909398</v>
+        <v>643694</v>
       </c>
       <c r="R8" t="n">
-        <v>7333290.90956175</v>
+        <v>7333058</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1420,19 +1325,9 @@
           <t>2014-08-19</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2014-08-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>55934767</v>
+        <v>55934770</v>
       </c>
       <c r="B9" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57791</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>102620</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>643503.0382949202</v>
+        <v>643689</v>
       </c>
       <c r="R9" t="n">
-        <v>7333437.154822675</v>
+        <v>7333291</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1532,19 +1422,9 @@
           <t>2014-08-19</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2014-08-19</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,118 +1448,6 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>55934776</v>
-      </c>
-      <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Gaddåive, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>643694.0119554366</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7333057.821087298</v>
-      </c>
-      <c r="S10" t="n">
-        <v>50</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2014-08-19</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2014-08-19</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Sture Westerberg</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Sture Westerberg, Robert Sandberg, Per-Anders Jonsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48673-2023 artfynd.xlsx
+++ b/artfynd/A 48673-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55934777</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55934771</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55934778</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55934768</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55934767</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55934776</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55934779</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,8 +1488,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55934770</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>